--- a/لیست حضور غیاب.xlsx
+++ b/لیست حضور غیاب.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fdmxf\Documents\GitHub\junior-soccer-assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152C0A2F-433B-4E7D-BA8A-EF7A2AF09BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA1D7A2-4E93-4A83-8E68-F3F64088264B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" activeTab="1" xr2:uid="{5569CC0C-4E0D-4071-9F05-C5A182EA12C3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{5569CC0C-4E0D-4071-9F05-C5A182EA12C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ATT" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="36">
   <si>
     <t>نام نام خانوادگی</t>
   </si>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>پارسا بابایی</t>
+  </si>
+  <si>
+    <t>اهورا ملک زاده</t>
   </si>
 </sst>
 </file>
@@ -615,6 +618,9 @@
       <c r="C3" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="D3" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A4" s="1" t="s">
@@ -626,6 +632,9 @@
       <c r="C4" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="D4" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A5" s="1" t="s">
@@ -637,6 +646,9 @@
       <c r="C5" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="D5" s="11" t="s">
+        <v>27</v>
+      </c>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="1.1000000000000001">
@@ -649,6 +661,9 @@
       <c r="C6" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="D6" s="12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A7" s="1" t="s">
@@ -660,6 +675,9 @@
       <c r="C7" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="D7" s="12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A8" s="1" t="s">
@@ -671,6 +689,9 @@
       <c r="C8" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="D8" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A9" s="1" t="s">
@@ -682,6 +703,9 @@
       <c r="C9" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="D9" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A10" s="1" t="s">
@@ -693,6 +717,9 @@
       <c r="C10" s="11" t="s">
         <v>27</v>
       </c>
+      <c r="D10" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A11" s="1" t="s">
@@ -713,6 +740,17 @@
         <v>26</v>
       </c>
       <c r="C12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="1.1000000000000001">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>27</v>
       </c>
     </row>
@@ -735,6 +773,9 @@
       <c r="C15" s="12" t="s">
         <v>27</v>
       </c>
+      <c r="D15" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="1.1000000000000001">
       <c r="A16" s="1" t="s">
@@ -743,8 +784,14 @@
       <c r="B16" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+      <c r="C16" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
@@ -754,16 +801,22 @@
       <c r="C17" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+      <c r="D17" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+      <c r="D18" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -771,7 +824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+    <row r="20" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -781,8 +834,11 @@
       <c r="C20" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+      <c r="D20" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
@@ -792,8 +848,11 @@
       <c r="C21" s="12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+      <c r="D21" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -803,8 +862,11 @@
       <c r="C22" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+      <c r="D22" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
@@ -814,13 +876,16 @@
       <c r="C23" s="11" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+      <c r="D23" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="C25" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="1.1000000000000001">
+    <row r="26" spans="1:4" x14ac:dyDescent="1.1000000000000001">
       <c r="C26" s="12" t="s">
         <v>27</v>
       </c>
